--- a/data/raw/sales/Week 34/White_Mulberry/Seller Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 34/White_Mulberry/Seller Sales (SP-API).xlsx
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
         <v>10672.88</v>
